--- a/src/tools/aptf-docs-vehicle-data-processing/Data/Tesla-Model3/2020-tesla-model3-uncertainity-analysis.xlsx
+++ b/src/tools/aptf-docs-vehicle-data-processing/Data/Tesla-Model3/2020-tesla-model3-uncertainity-analysis.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="72F_Cycle_Data_Hioki" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="wh_cal_62005016" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -164,178 +162,1716 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SUMMARY (cycle totals)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>No-cycle</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>UDDS 1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>UDDS 2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Highway</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>US06</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UDDS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Energy [Wh]</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>60.73126551761756</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1486.303700991428</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1349.76572866279</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1954.712959543047</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2032.235503559502</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>6883.749158274386</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Test ID [#]</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Sub-Phase</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Cycle Distance [mi]</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Start SOC</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>End SOC</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV Batt (500A)
+Start 
+WP1 [Wh]
+</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt Out (500A) End
+WP1 [Wh]</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A)
+Δ [Wh]</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A) Energy consumption
+[Wh/mi]</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Start WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A)  End WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) 
+Δ WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Δ WP2 [Wh/mi]</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Recharge Allocation Factor</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>u (Energy)</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11.44305942931166</v>
+        <v>62005016</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>25.79406295346998</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>25.33118005031979</v>
+        <v>7.46</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.29999535840068</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>16.10832426245825</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>85.53356262464871</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1512</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1491</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>199.73</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1507</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>198.93</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>u (Energy) [%]</t>
-        </is>
-      </c>
+      <c r="A4" s="3" t="n"/>
       <c r="B4" s="2" t="n">
-        <v>18.84212247477725</v>
+        <v>62005016</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.735450361609423</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.876709380924594</v>
+        <v>7.47</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9361985998536925</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.79264062822661</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.242543280674832</v>
-      </c>
+        <v>3515</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>4867</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1352</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>181.02</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>3507</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>4857</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1350</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>180.76</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>u_sqrt (Energy)</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="n"/>
       <c r="B5" s="2" t="n">
-        <v>0.1322510312977808</v>
+        <v>62005018</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.2441131264667169</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2427490579829497</v>
+        <v>7.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.2239767902808438</v>
+        <v>15.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.2820077239033389</v>
+        <v>14.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.9928466986338492</v>
-      </c>
+        <v>67034</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>68307</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>170.61</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>67029</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>68302</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>170.61</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>u_sqrt (Energy) [%]</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="n"/>
       <c r="B6" s="2" t="n">
-        <v>0.2177643264479908</v>
+        <v>62005018</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.01642417537572456</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.01798453263615165</v>
+        <v>7.46</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.01145829566368674</v>
+        <v>11.3</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.01387672459266638</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.01442305168020874</v>
-      </c>
+        <v>70214</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>71474</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>70209</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>71469</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>62006032</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1539</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1517</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>203.41</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1543</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>203.95</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="2" t="n">
+        <v>62006032</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>3518</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>4820</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1302</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>174.56</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>3525</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>4830</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>174.96</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="2" t="n">
+        <v>62006034</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>65678</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>66928</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>167.59</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>65749</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>67000</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1251</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>167.72</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>62006034</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>68814</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>70058</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1244</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>166.79</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>68888</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>70134</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>167.06</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HWY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Test ID [#]</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Sub-Phase</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Cycle Distance [mi]</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Start SOC</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>End SOC</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV Batt (500A)
+Start 
+WP1 [Wh]
+</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt Out (500A) End
+WP1 [Wh]</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A)
+Δ [Wh]</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A) Energy consumption
+[Wh/mi]</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Start WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A)  End WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) 
+Δ WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Δ WP2 [Wh/mi]</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>Recharge Allocation Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>62005016</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1514</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>3470</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>190.03</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1509</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>3464</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1955</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>189.93</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>62005018</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>68309</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>70174</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1865</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>181.35</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>68304</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>70169</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1865</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>181.35</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>62006032</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>3476</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1935</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>188.16</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1545</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>3482</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1937</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>188.35</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>62006034</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>66930</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>68775</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1845</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>67001</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>68848</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1847</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>179.59</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>US06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Test ID [#]</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Sub-Phase</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Cycle Distance [mi]</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Start SOC</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>End SOC</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV Batt (500A)
+Start 
+WP1 [Wh]
+</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt Out (500A) End
+WP1 [Wh]</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A)
+Δ [Wh]</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A) Energy consumption
+[Wh/mi]</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Start WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A)  End WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) 
+Δ WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Δ WP2 [Wh/mi]</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>Recharge Allocation Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>62005016</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>4879</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>6751</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>252.95</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>4868</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>6740</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>252.95</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>62005018</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>65043</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>66841</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1949</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>242.8</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>65039</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>66837</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1949</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>242.8</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>62006032</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>4830</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>6676</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>248.83</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>4839</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>6687</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>249.2</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>62006034</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>63728</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>65492</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1911</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>238.11</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>63798</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>65562</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1912</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>238.23</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSS 65MPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>Test ID [#]</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>Sub-Phase</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>Cycle Distance [mi]</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Start SOC</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>End SOC</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV Batt (500A)
+Start 
+WP1 [Wh]
+</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt Out (500A) End
+WP1 [Wh]</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A)
+Δ [Wh]</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A) Energy consumption
+[Wh/mi]</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Start WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A)  End WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) 
+Δ WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Δ WP2 [Wh/mi]</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>Recharge Allocation Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>62005017</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
+        <v>257.3</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>7020</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>64989</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>57969</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>7005</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>64987</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>57982</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>225.35</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="2" t="n">
+        <v>62005019</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>71501</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>76421</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>4920</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>223.57</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>71495</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>76416</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>4921</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>62006033</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="n">
+        <v>254.77</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>6857</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>63703</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>56846</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>223.13</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>6869</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>63773</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>56904</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>223.35</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="2" t="n">
+        <v>62006035</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>70076</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>76123</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>6047</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>221.93</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>70153</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>76203</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>6050</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>222.04</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHARGE L2 23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Test ID [#]</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Sub-Phase</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Cycle Distance [mi]</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Start SOC</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>End SOC</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV Batt (500A)
+Start 
+WP1 [Wh]
+</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt Out (500A) End
+WP1 [Wh]</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A)
+Δ [Wh]</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (500A) Energy consumption
+[Wh/mi]</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Start WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A)  End WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) 
+Δ WP2 [Wh]</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>HV Batt (1000A) Δ WP2 [Wh/mi]</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>Recharge Allocation Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>62005020</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>76422</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>-3403</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-79825</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>-8072900.34</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>76417</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>-3488</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-79905</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-8080990.94</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>62006036</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="n">
+        <v>76125</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>-2861</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-78986</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>76204</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>-2797</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-79001</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A35"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A36"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A21:A22"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>